--- a/feedback_forms/004_support_satisfaction_survey--feedback_forms.xlsx
+++ b/feedback_forms/004_support_satisfaction_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How did you contact us?</t>
+          <t>Contact Method</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>contact_time</t>
+          <t>contact_time_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>resolution_time</t>
+          <t>resolution_time_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>support_rating</t>
+          <t>support_rating_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>resolution_method</t>
+          <t>resolution_method_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>follow_up_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>follow_up_details</t>
+          <t>follow_up_details_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Follow Up</t>
+          <t>Follow Up Details 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>resolution_method_choices</t>
+          <t>resolution_method_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>resolution_method_choices</t>
+          <t>resolution_method_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>resolution_method_choices</t>
+          <t>resolution_method_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>resolution_method_choices</t>
+          <t>resolution_method_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>resolution_method_choices</t>
+          <t>resolution_method_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>follow_up_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>follow_up_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
